--- a/Closoft_CSharp_Basics_Curriculum.xlsx
+++ b/Closoft_CSharp_Basics_Curriculum.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://closoft.sharepoint.com/sites/All-Sales/Shared Documents/Sales/8. Training and Development (Tech)/C Sharp/Topics to be Covered/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainings\TrainingCamp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{52A16E34-72D6-434C-8E06-D13196DD9E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B48C7C5-419E-4DA2-BA84-9FE067D85D54}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F3085A-F573-4BEB-BE49-D9E501909A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Curriculum" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -344,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,6 +353,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -533,6 +538,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -848,14 +859,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C80"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="1"/>
-    <col min="2" max="2" width="41.90625" customWidth="1"/>
-    <col min="3" max="3" width="47.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="1"/>
+    <col min="2" max="2" width="41.88671875" customWidth="1"/>
+    <col min="3" max="3" width="47.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>95</v>
       </c>
@@ -866,214 +877,214 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="13"/>
-      <c r="B3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="19"/>
+      <c r="B3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="13"/>
-      <c r="B4" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="19"/>
+      <c r="B4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="13"/>
-      <c r="B5" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="13"/>
-      <c r="B6" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="14"/>
-      <c r="B7" s="9" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="20"/>
+      <c r="B7" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="19"/>
+      <c r="B10" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="19"/>
+      <c r="B11" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="19"/>
+      <c r="B12" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="14"/>
-      <c r="B13" s="9" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="20"/>
+      <c r="B13" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="12">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="18">
         <v>3</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="19"/>
+      <c r="B15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="19"/>
+      <c r="B16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="14"/>
-      <c r="B17" s="9" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="20"/>
+      <c r="B17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="12">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="18">
         <v>4</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="19"/>
+      <c r="B19" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="19"/>
+      <c r="B20" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="19"/>
+      <c r="B22" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="19"/>
+      <c r="B23" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="19"/>
       <c r="B24" t="s">
         <v>21</v>
       </c>
@@ -1081,17 +1092,17 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="14"/>
-      <c r="B25" s="9" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="20"/>
+      <c r="B25" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="12">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="18">
         <v>5</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -1101,8 +1112,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="19"/>
       <c r="B27" t="s">
         <v>30</v>
       </c>
@@ -1110,8 +1121,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="19"/>
       <c r="B28" t="s">
         <v>30</v>
       </c>
@@ -1119,8 +1130,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="19"/>
       <c r="B29" t="s">
         <v>30</v>
       </c>
@@ -1128,8 +1139,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="14"/>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="20"/>
       <c r="B30" s="9" t="s">
         <v>30</v>
       </c>
@@ -1137,37 +1148,37 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="18">
         <v>6</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="19"/>
+      <c r="B32" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="19"/>
+      <c r="B33" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="14"/>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="20"/>
       <c r="B34" s="9" t="s">
         <v>36</v>
       </c>
@@ -1175,8 +1186,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="18">
         <v>7</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -1186,8 +1197,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="19"/>
       <c r="B36" t="s">
         <v>41</v>
       </c>
@@ -1195,8 +1206,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="14"/>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="20"/>
       <c r="B37" s="9" t="s">
         <v>41</v>
       </c>
@@ -1204,8 +1215,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="12">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="18">
         <v>8</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -1215,8 +1226,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="14"/>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="20"/>
       <c r="B39" s="9" t="s">
         <v>45</v>
       </c>
@@ -1224,8 +1235,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="12">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="18">
         <v>9</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -1235,8 +1246,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="19"/>
       <c r="B41" t="s">
         <v>48</v>
       </c>
@@ -1244,8 +1255,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="19"/>
       <c r="B42" t="s">
         <v>48</v>
       </c>
@@ -1253,8 +1264,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="19"/>
       <c r="B43" t="s">
         <v>48</v>
       </c>
@@ -1262,8 +1273,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="14"/>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="20"/>
       <c r="B44" s="9" t="s">
         <v>48</v>
       </c>
@@ -1271,8 +1282,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="18">
         <v>10</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -1282,8 +1293,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="19"/>
       <c r="B46" t="s">
         <v>54</v>
       </c>
@@ -1291,8 +1302,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="19"/>
       <c r="B47" t="s">
         <v>54</v>
       </c>
@@ -1300,8 +1311,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="19"/>
       <c r="B48" t="s">
         <v>54</v>
       </c>
@@ -1309,8 +1320,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="19"/>
       <c r="B49" t="s">
         <v>54</v>
       </c>
@@ -1318,8 +1329,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="19"/>
       <c r="B50" t="s">
         <v>54</v>
       </c>
@@ -1327,8 +1338,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="14"/>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="20"/>
       <c r="B51" s="9" t="s">
         <v>54</v>
       </c>
@@ -1336,8 +1347,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="18">
         <v>11</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -1347,8 +1358,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="19"/>
       <c r="B53" t="s">
         <v>92</v>
       </c>
@@ -1356,8 +1367,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="19"/>
       <c r="B54" t="s">
         <v>92</v>
       </c>
@@ -1365,8 +1376,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="19"/>
       <c r="B55" t="s">
         <v>92</v>
       </c>
@@ -1374,8 +1385,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="14"/>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="20"/>
       <c r="B56" s="9" t="s">
         <v>92</v>
       </c>
@@ -1383,8 +1394,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="18">
         <v>12</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -1394,8 +1405,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="19"/>
       <c r="B58" t="s">
         <v>65</v>
       </c>
@@ -1403,8 +1414,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="19"/>
       <c r="B59" t="s">
         <v>65</v>
       </c>
@@ -1412,8 +1423,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="19"/>
       <c r="B60" t="s">
         <v>65</v>
       </c>
@@ -1421,8 +1432,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="19"/>
       <c r="B61" t="s">
         <v>65</v>
       </c>
@@ -1430,8 +1441,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="19"/>
       <c r="B62" t="s">
         <v>65</v>
       </c>
@@ -1439,8 +1450,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="14"/>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="20"/>
       <c r="B63" s="9" t="s">
         <v>65</v>
       </c>
@@ -1448,8 +1459,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="18">
         <v>13</v>
       </c>
       <c r="B64" s="8" t="s">
@@ -1459,8 +1470,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="19"/>
       <c r="B65" t="s">
         <v>73</v>
       </c>
@@ -1468,8 +1479,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="19"/>
       <c r="B66" t="s">
         <v>73</v>
       </c>
@@ -1477,8 +1488,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="13"/>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="19"/>
       <c r="B67" t="s">
         <v>73</v>
       </c>
@@ -1486,8 +1497,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="13"/>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="19"/>
       <c r="B68" t="s">
         <v>73</v>
       </c>
@@ -1495,8 +1506,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="19"/>
       <c r="B69" t="s">
         <v>73</v>
       </c>
@@ -1504,8 +1515,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="13"/>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="19"/>
       <c r="B70" t="s">
         <v>73</v>
       </c>
@@ -1513,8 +1524,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="13"/>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="19"/>
       <c r="B71" t="s">
         <v>73</v>
       </c>
@@ -1522,8 +1533,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="14"/>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="20"/>
       <c r="B72" s="9" t="s">
         <v>73</v>
       </c>
@@ -1531,19 +1542,19 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="12">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="18">
         <v>14</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C73" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="13"/>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="19"/>
       <c r="B74" t="s">
         <v>83</v>
       </c>
@@ -1551,8 +1562,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="13"/>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="19"/>
       <c r="B75" t="s">
         <v>83</v>
       </c>
@@ -1560,8 +1571,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="13"/>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="19"/>
       <c r="B76" t="s">
         <v>83</v>
       </c>
@@ -1569,8 +1580,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="13"/>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="19"/>
       <c r="B77" t="s">
         <v>83</v>
       </c>
@@ -1578,8 +1589,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="13"/>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="19"/>
       <c r="B78" t="s">
         <v>83</v>
       </c>
@@ -1587,8 +1598,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="13"/>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="19"/>
       <c r="B79" t="s">
         <v>83</v>
       </c>
@@ -1596,8 +1607,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="15"/>
+    <row r="80" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="21"/>
       <c r="B80" s="6" t="s">
         <v>83</v>
       </c>
@@ -1628,6 +1639,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed8985c6-480d-4c9d-9165-b82c62bd8676">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086F7701EFF7F53498CE751378C5A02C8" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e04659cc8ebb3c0a66676b1e84b49b8d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ed8985c6-480d-4c9d-9165-b82c62bd8676" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74a296adf5f90f002f0fe4f1aa63d8be" ns2:_="">
     <xsd:import namespace="ed8985c6-480d-4c9d-9165-b82c62bd8676"/>
@@ -1817,26 +1847,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170E41E9-2F1F-473E-9C8B-048775B63688}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed8985c6-480d-4c9d-9165-b82c62bd8676">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66CE17AB-0086-4CF8-8909-56E7FF77C6DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ed8985c6-480d-4c9d-9165-b82c62bd8676"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{969BFCE1-7F1A-42B7-802A-0D9B9BC44299}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1852,22 +1881,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170E41E9-2F1F-473E-9C8B-048775B63688}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66CE17AB-0086-4CF8-8909-56E7FF77C6DB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ed8985c6-480d-4c9d-9165-b82c62bd8676"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Closoft_CSharp_Basics_Curriculum.xlsx
+++ b/Closoft_CSharp_Basics_Curriculum.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainings\TrainingCamp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F3085A-F573-4BEB-BE49-D9E501909A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6719C29-B573-4811-B8F2-2581F0D96447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Curriculum" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="97">
   <si>
     <t>Category</t>
   </si>
@@ -320,6 +319,9 @@
   </si>
   <si>
     <t>Section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inheritance, Polymorphism and Encapsulation. </t>
   </si>
 </sst>
 </file>
@@ -858,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -1085,10 +1087,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="19"/>
-      <c r="B24" t="s">
+      <c r="B24" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="13" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1105,46 +1107,46 @@
       <c r="A26" s="18">
         <v>5</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="19"/>
-      <c r="B27" t="s">
+      <c r="B27" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="19"/>
-      <c r="B28" t="s">
+      <c r="B28" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="13" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="19"/>
-      <c r="B29" t="s">
+      <c r="B29" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="20"/>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="14" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1179,10 +1181,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="20"/>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="14" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1190,28 +1192,28 @@
       <c r="A35" s="18">
         <v>7</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="19"/>
-      <c r="B36" t="s">
+      <c r="B36" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="20"/>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="14" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1239,67 +1241,65 @@
       <c r="A40" s="18">
         <v>9</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="19"/>
-      <c r="B41" t="s">
+      <c r="B41" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="13" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="19"/>
-      <c r="B42" t="s">
+      <c r="B42" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="13" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="19"/>
-      <c r="B43" t="s">
+      <c r="B43" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="20"/>
-      <c r="B44" s="9" t="s">
+      <c r="A44" s="19"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="20"/>
+      <c r="B45" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C45" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="18">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="18">
         <v>10</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B46" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C46" s="10" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -1308,7 +1308,7 @@
         <v>54</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -1317,7 +1317,7 @@
         <v>54</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -1326,7 +1326,7 @@
         <v>54</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -1335,36 +1335,36 @@
         <v>54</v>
       </c>
       <c r="C50" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="19"/>
+      <c r="B51" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="20"/>
-      <c r="B51" s="9" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="20"/>
+      <c r="B52" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C52" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="18">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="18">
         <v>11</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B53" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C53" s="10" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
-      <c r="B53" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -1373,7 +1373,7 @@
         <v>92</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -1382,36 +1382,36 @@
         <v>92</v>
       </c>
       <c r="C55" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="19"/>
+      <c r="B56" t="s">
+        <v>92</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="20"/>
-      <c r="B56" s="9" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="20"/>
+      <c r="B57" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C57" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="18">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="18">
         <v>12</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B58" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C58" s="10" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="19"/>
-      <c r="B58" t="s">
-        <v>65</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1420,7 +1420,7 @@
         <v>65</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -1429,7 +1429,7 @@
         <v>65</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -1438,7 +1438,7 @@
         <v>65</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1447,72 +1447,72 @@
         <v>65</v>
       </c>
       <c r="C62" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="19"/>
+      <c r="B63" t="s">
+        <v>65</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="20"/>
-      <c r="B63" s="9" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="20"/>
+      <c r="B64" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C64" s="11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="18">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="18">
         <v>13</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B65" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C65" s="12" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="19"/>
-      <c r="B65" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="19"/>
-      <c r="B66" t="s">
+      <c r="B66" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>76</v>
+      <c r="C66" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="19"/>
-      <c r="B67" t="s">
+      <c r="B67" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>77</v>
+      <c r="C67" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="19"/>
-      <c r="B68" t="s">
+      <c r="B68" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>78</v>
+      <c r="C68" s="13" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="19"/>
-      <c r="B69" t="s">
+      <c r="B69" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>79</v>
+      <c r="C69" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1521,63 +1521,63 @@
         <v>73</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="19"/>
-      <c r="B71" t="s">
+      <c r="B71" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="19"/>
+      <c r="B72" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="20"/>
-      <c r="B72" s="9" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="20"/>
+      <c r="B73" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C73" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="18">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="18">
         <v>14</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B74" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C74" s="12" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="19"/>
-      <c r="B74" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="19"/>
-      <c r="B75" t="s">
+      <c r="B75" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>86</v>
+      <c r="C75" s="13" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="19"/>
-      <c r="B76" t="s">
+      <c r="B76" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>87</v>
+      <c r="C76" s="13" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -1586,16 +1586,16 @@
         <v>83</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="19"/>
-      <c r="B78" t="s">
+      <c r="B78" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>89</v>
+      <c r="C78" s="13" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -1604,34 +1604,43 @@
         <v>83</v>
       </c>
       <c r="C79" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="19"/>
+      <c r="B80" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="21"/>
-      <c r="B80" s="6" t="s">
+    <row r="81" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="21"/>
+      <c r="B81" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C81" s="7" t="s">
         <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A65:A73"/>
+    <mergeCell ref="A74:A81"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="A58:A64"/>
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A8:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A25"/>
     <mergeCell ref="A26:A30"/>
-    <mergeCell ref="A64:A72"/>
-    <mergeCell ref="A73:A80"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A44"/>
-    <mergeCell ref="A45:A51"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="A57:A63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1648,16 +1657,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed8985c6-480d-4c9d-9165-b82c62bd8676">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086F7701EFF7F53498CE751378C5A02C8" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e04659cc8ebb3c0a66676b1e84b49b8d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ed8985c6-480d-4c9d-9165-b82c62bd8676" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74a296adf5f90f002f0fe4f1aa63d8be" ns2:_="">
     <xsd:import namespace="ed8985c6-480d-4c9d-9165-b82c62bd8676"/>
@@ -1847,6 +1846,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed8985c6-480d-4c9d-9165-b82c62bd8676">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170E41E9-2F1F-473E-9C8B-048775B63688}">
   <ds:schemaRefs>
@@ -1856,16 +1865,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66CE17AB-0086-4CF8-8909-56E7FF77C6DB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ed8985c6-480d-4c9d-9165-b82c62bd8676"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{969BFCE1-7F1A-42B7-802A-0D9B9BC44299}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1881,4 +1880,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66CE17AB-0086-4CF8-8909-56E7FF77C6DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ed8985c6-480d-4c9d-9165-b82c62bd8676"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Closoft_CSharp_Basics_Curriculum.xlsx
+++ b/Closoft_CSharp_Basics_Curriculum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainings\TrainingCamp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6719C29-B573-4811-B8F2-2581F0D96447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD8D54B-3034-4CDE-9ADD-D7CA65E18FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Curriculum" sheetId="1" r:id="rId1"/>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="19"/>
-      <c r="B79" t="s">
+      <c r="B79" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="13" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1627,6 +1627,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A25"/>
+    <mergeCell ref="A26:A30"/>
     <mergeCell ref="A65:A73"/>
     <mergeCell ref="A74:A81"/>
     <mergeCell ref="A35:A37"/>
@@ -1635,12 +1641,6 @@
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A57"/>
     <mergeCell ref="A58:A64"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A25"/>
-    <mergeCell ref="A26:A30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1648,15 +1648,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086F7701EFF7F53498CE751378C5A02C8" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e04659cc8ebb3c0a66676b1e84b49b8d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ed8985c6-480d-4c9d-9165-b82c62bd8676" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74a296adf5f90f002f0fe4f1aa63d8be" ns2:_="">
     <xsd:import namespace="ed8985c6-480d-4c9d-9165-b82c62bd8676"/>
@@ -1846,6 +1837,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1857,14 +1857,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170E41E9-2F1F-473E-9C8B-048775B63688}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{969BFCE1-7F1A-42B7-802A-0D9B9BC44299}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1882,6 +1874,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170E41E9-2F1F-473E-9C8B-048775B63688}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66CE17AB-0086-4CF8-8909-56E7FF77C6DB}">
   <ds:schemaRefs>
